--- a/2022 data/excel_outputs/156_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/156_boothwise_data.xlsx
@@ -14,11 +14,71 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="489">
   <si>
     <t>AC 156 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -193,7 +253,7 @@
     <t>P P BHETA DHEERA ROOM NO 02</t>
   </si>
   <si>
-    <t>P P BHETA DHEERA ROOM NO ■■</t>
+    <t>CH CH BHMEDAMCHANAT</t>
   </si>
   <si>
     <t>SANSKRIT MAHAVIDYALAYA SAKAHA ROOM NO 01</t>
@@ -253,7 +313,7 @@
     <t>P P MUJAHIDPUR ROOM NO 01</t>
   </si>
   <si>
-    <t>P P MUJAHIDPUR ROOM NO 0■</t>
+    <t>CH CH AIMUNAKIM</t>
   </si>
   <si>
     <t>P P TERIYA ROOM NO 01</t>
@@ -1072,7 +1132,7 @@
     <t>JHS BHITHARI</t>
   </si>
   <si>
-    <t>P P MAJHRETA ROOM NO ■■</t>
+    <t>CH CH DAMLAPALAMD TVAVAU CHAVAN 0 1</t>
   </si>
   <si>
     <t>P P MAJHRETA ROOM N0 02</t>
@@ -1090,7 +1150,7 @@
     <t>P P SAKATPUR ROOM 01</t>
   </si>
   <si>
-    <t>P P SAKATPUR ROOM 0■</t>
+    <t>BBH BBH |PCH|NDACH K|T SHRCH|CH|JMD|AI|CH BBH|D|CH|K DAL|SHR|J|D JT|T|N</t>
   </si>
   <si>
     <t>P P BARKHERA ROOM 01</t>
@@ -1291,7 +1351,7 @@
     <t>P P KAKWAHI ROOM 01</t>
   </si>
   <si>
-    <t>P P KAKHWAHI ROOM 0■</t>
+    <t>P P KAKWAHI ROOM NO. 424</t>
   </si>
   <si>
     <t>P P MENDUA ROOM NO 01</t>
@@ -1427,8 +1487,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1444,7 +1512,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1452,12 +1520,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1756,73 +1842,133 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="D2" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="E2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="F2" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="G2" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="H2" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="I2" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="J2" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="K2" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="L2" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="M2" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="N2" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="O2" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="P2" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="Q2" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="R2" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="S2" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="T2" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="U2" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -1830,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>1159</v>
@@ -1895,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>925</v>
@@ -1960,7 +2106,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>841</v>
@@ -2025,7 +2171,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>655</v>
@@ -2090,7 +2236,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>588</v>
@@ -2155,7 +2301,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>1117</v>
@@ -2220,7 +2366,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>704</v>
@@ -2285,7 +2431,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>418</v>
@@ -2350,7 +2496,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>589</v>
@@ -2415,7 +2561,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>819</v>
@@ -2480,7 +2626,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>549</v>
@@ -2545,7 +2691,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>882</v>
@@ -2610,7 +2756,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>403</v>
@@ -2675,7 +2821,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>1024</v>
@@ -2740,7 +2886,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>600</v>
@@ -2805,7 +2951,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <v>719</v>
@@ -2870,7 +3016,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>783</v>
@@ -2935,7 +3081,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>470</v>
@@ -3000,7 +3146,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>311</v>
@@ -3065,7 +3211,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>861</v>
@@ -3130,7 +3276,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C23">
         <v>558</v>
@@ -3195,7 +3341,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>575</v>
@@ -3260,7 +3406,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>588</v>
@@ -3325,7 +3471,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>587</v>
@@ -3390,7 +3536,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>618</v>
@@ -3455,7 +3601,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>905</v>
@@ -3520,7 +3666,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>1016</v>
@@ -3585,7 +3731,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>722</v>
@@ -3650,7 +3796,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>707</v>
@@ -3715,7 +3861,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>489</v>
@@ -3780,7 +3926,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>655</v>
@@ -3845,7 +3991,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <v>465</v>
@@ -3910,7 +4056,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C35">
         <v>687</v>
@@ -3975,7 +4121,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C36">
         <v>1082</v>
@@ -4040,7 +4186,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C37">
         <v>995</v>
@@ -4105,7 +4251,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <v>817</v>
@@ -4170,7 +4316,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C39">
         <v>793</v>
@@ -4235,7 +4381,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C40">
         <v>743</v>
@@ -4300,7 +4446,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>840</v>
@@ -4365,7 +4511,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C42">
         <v>966</v>
@@ -4430,7 +4576,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <v>887</v>
@@ -4495,7 +4641,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C44">
         <v>712</v>
@@ -4560,7 +4706,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>1111</v>
@@ -4625,7 +4771,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C46">
         <v>611</v>
@@ -4690,7 +4836,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C47">
         <v>915</v>
@@ -4755,7 +4901,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <v>647</v>
@@ -4820,7 +4966,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C49">
         <v>778</v>
@@ -4885,7 +5031,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C50">
         <v>910</v>
@@ -4950,7 +5096,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C51">
         <v>712</v>
@@ -5015,7 +5161,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C52">
         <v>1151</v>
@@ -5080,7 +5226,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C53">
         <v>941</v>
@@ -5145,7 +5291,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C54">
         <v>1091</v>
@@ -5210,7 +5356,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>745</v>
@@ -5275,7 +5421,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C56">
         <v>917</v>
@@ -5340,7 +5486,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C57">
         <v>1107</v>
@@ -5405,7 +5551,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>791</v>
@@ -5470,7 +5616,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C59">
         <v>725</v>
@@ -5535,7 +5681,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C60">
         <v>792</v>
@@ -5600,7 +5746,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C61">
         <v>667</v>
@@ -5665,7 +5811,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C62">
         <v>1074</v>
@@ -5730,7 +5876,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C63">
         <v>831</v>
@@ -5795,7 +5941,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C64">
         <v>888</v>
@@ -5860,7 +6006,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C65">
         <v>941</v>
@@ -5925,7 +6071,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C66">
         <v>1004</v>
@@ -5990,7 +6136,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C67">
         <v>1131</v>
@@ -6055,7 +6201,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C68">
         <v>833</v>
@@ -6120,7 +6266,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C69">
         <v>577</v>
@@ -6185,7 +6331,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C70">
         <v>616</v>
@@ -6250,7 +6396,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C71">
         <v>650</v>
@@ -6315,7 +6461,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C72">
         <v>653</v>
@@ -6380,7 +6526,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C73">
         <v>1021</v>
@@ -6445,7 +6591,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C74">
         <v>1205</v>
@@ -6510,7 +6656,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C75">
         <v>511</v>
@@ -6575,7 +6721,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C76">
         <v>1092</v>
@@ -6640,7 +6786,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C77">
         <v>578</v>
@@ -6705,7 +6851,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C78">
         <v>814</v>
@@ -6770,7 +6916,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C79">
         <v>671</v>
@@ -6835,7 +6981,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C80">
         <v>638</v>
@@ -6900,7 +7046,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C81">
         <v>818</v>
@@ -6965,7 +7111,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C82">
         <v>968</v>
@@ -7030,7 +7176,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C83">
         <v>1153</v>
@@ -7095,7 +7241,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C84">
         <v>920</v>
@@ -7160,7 +7306,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C85">
         <v>750</v>
@@ -7225,7 +7371,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C86">
         <v>957</v>
@@ -7290,7 +7436,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C87">
         <v>1084</v>
@@ -7355,7 +7501,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C88">
         <v>1105</v>
@@ -7420,7 +7566,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C89">
         <v>1050</v>
@@ -7485,7 +7631,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C90">
         <v>1043</v>
@@ -7550,7 +7696,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C91">
         <v>411</v>
@@ -7615,7 +7761,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C92">
         <v>1079</v>
@@ -7680,7 +7826,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C93">
         <v>675</v>
@@ -7745,7 +7891,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C94">
         <v>1182</v>
@@ -7810,7 +7956,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C95">
         <v>880</v>
@@ -7875,7 +8021,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C96">
         <v>1121</v>
@@ -7940,7 +8086,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C97">
         <v>1005</v>
@@ -8005,7 +8151,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C98">
         <v>765</v>
@@ -8070,7 +8216,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C99">
         <v>1197</v>
@@ -8135,7 +8281,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C100">
         <v>904</v>
@@ -8200,7 +8346,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C101">
         <v>1038</v>
@@ -8265,7 +8411,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C102">
         <v>839</v>
@@ -8330,7 +8476,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C103">
         <v>1108</v>
@@ -8395,7 +8541,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C104">
         <v>523</v>
@@ -8460,7 +8606,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C105">
         <v>1040</v>
@@ -8525,7 +8671,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C106">
         <v>1062</v>
@@ -8590,7 +8736,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C107">
         <v>909</v>
@@ -8655,7 +8801,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C108">
         <v>1135</v>
@@ -8720,7 +8866,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C109">
         <v>908</v>
@@ -8785,7 +8931,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C110">
         <v>1197</v>
@@ -8850,7 +8996,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C111">
         <v>1023</v>
@@ -8915,7 +9061,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C112">
         <v>944</v>
@@ -8980,7 +9126,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C113">
         <v>741</v>
@@ -9045,7 +9191,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C114">
         <v>774</v>
@@ -9110,7 +9256,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C115">
         <v>901</v>
@@ -9175,7 +9321,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C116">
         <v>811</v>
@@ -9240,7 +9386,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C117">
         <v>444</v>
@@ -9305,7 +9451,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C118">
         <v>1063</v>
@@ -9370,7 +9516,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C119">
         <v>967</v>
@@ -9435,7 +9581,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C120">
         <v>1103</v>
@@ -9500,7 +9646,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C121">
         <v>623</v>
@@ -9565,7 +9711,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C122">
         <v>621</v>
@@ -9630,7 +9776,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C123">
         <v>1178</v>
@@ -9695,7 +9841,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C124">
         <v>959</v>
@@ -9760,7 +9906,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C125">
         <v>923</v>
@@ -9825,7 +9971,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C126">
         <v>892</v>
@@ -9890,7 +10036,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C127">
         <v>646</v>
@@ -9955,7 +10101,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C128">
         <v>972</v>
@@ -10020,7 +10166,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="C129">
         <v>839</v>
@@ -10085,7 +10231,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="C130">
         <v>1067</v>
@@ -10150,7 +10296,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C131">
         <v>931</v>
@@ -10215,7 +10361,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="C132">
         <v>900</v>
@@ -10280,7 +10426,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="C133">
         <v>686</v>
@@ -10345,7 +10491,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="C134">
         <v>888</v>
@@ -10410,7 +10556,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C135">
         <v>822</v>
@@ -10475,7 +10621,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C136">
         <v>1134</v>
@@ -10540,7 +10686,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="C137">
         <v>1095</v>
@@ -10605,7 +10751,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C138">
         <v>902</v>
@@ -10670,7 +10816,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="C139">
         <v>848</v>
@@ -10735,7 +10881,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C140">
         <v>916</v>
@@ -10800,7 +10946,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C141">
         <v>1010</v>
@@ -10865,7 +11011,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C142">
         <v>888</v>
@@ -10930,7 +11076,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C143">
         <v>1212</v>
@@ -10995,7 +11141,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C144">
         <v>625</v>
@@ -11060,7 +11206,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C145">
         <v>1126</v>
@@ -11125,7 +11271,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="C146">
         <v>1166</v>
@@ -11190,7 +11336,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C147">
         <v>725</v>
@@ -11255,7 +11401,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>699</v>
@@ -11320,7 +11466,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>723</v>
@@ -11385,7 +11531,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>706</v>
@@ -11450,7 +11596,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C151">
         <v>828</v>
@@ -11515,7 +11661,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>392</v>
@@ -11580,7 +11726,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="C153">
         <v>771</v>
@@ -11645,7 +11791,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C154">
         <v>911</v>
@@ -11710,7 +11856,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>926</v>
@@ -11775,7 +11921,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C156">
         <v>1131</v>
@@ -11840,7 +11986,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C157">
         <v>870</v>
@@ -11905,7 +12051,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="C158">
         <v>581</v>
@@ -11970,7 +12116,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C159">
         <v>852</v>
@@ -12035,7 +12181,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C160">
         <v>512</v>
@@ -12100,7 +12246,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C161">
         <v>1141</v>
@@ -12165,7 +12311,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="C162">
         <v>1130</v>
@@ -12230,7 +12376,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="C163">
         <v>1161</v>
@@ -12295,7 +12441,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C164">
         <v>911</v>
@@ -12360,7 +12506,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>852</v>
@@ -12425,7 +12571,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C166">
         <v>878</v>
@@ -12490,7 +12636,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="C167">
         <v>872</v>
@@ -12555,7 +12701,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="C168">
         <v>1017</v>
@@ -12620,7 +12766,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C169">
         <v>1132</v>
@@ -12685,7 +12831,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C170">
         <v>1244</v>
@@ -12750,7 +12896,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="C171">
         <v>1130</v>
@@ -12815,7 +12961,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C172">
         <v>996</v>
@@ -12880,7 +13026,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C173">
         <v>926</v>
@@ -12945,7 +13091,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C174">
         <v>793</v>
@@ -13010,7 +13156,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="C175">
         <v>1011</v>
@@ -13075,7 +13221,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C176">
         <v>1184</v>
@@ -13140,7 +13286,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="C177">
         <v>806</v>
@@ -13205,7 +13351,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="C178">
         <v>814</v>
@@ -13270,7 +13416,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C179">
         <v>933</v>
@@ -13335,7 +13481,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C180">
         <v>1028</v>
@@ -13400,7 +13546,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C181">
         <v>951</v>
@@ -13465,7 +13611,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C182">
         <v>919</v>
@@ -13530,7 +13676,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C183">
         <v>1017</v>
@@ -13595,7 +13741,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C184">
         <v>1019</v>
@@ -13660,7 +13806,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="C185">
         <v>996</v>
@@ -13725,7 +13871,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C186">
         <v>832</v>
@@ -13790,7 +13936,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="C187">
         <v>884</v>
@@ -13855,7 +14001,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C188">
         <v>921</v>
@@ -13920,7 +14066,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C189">
         <v>898</v>
@@ -13985,7 +14131,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="C190">
         <v>937</v>
@@ -14050,7 +14196,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C191">
         <v>1099</v>
@@ -14115,7 +14261,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="C192">
         <v>1138</v>
@@ -14180,7 +14326,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C193">
         <v>1087</v>
@@ -14245,7 +14391,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C194">
         <v>803</v>
@@ -14310,7 +14456,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C195">
         <v>1111</v>
@@ -14375,7 +14521,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C196">
         <v>1094</v>
@@ -14440,7 +14586,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="C197">
         <v>756</v>
@@ -14505,7 +14651,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="C198">
         <v>1120</v>
@@ -14570,7 +14716,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="C199">
         <v>1025</v>
@@ -14635,7 +14781,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C200">
         <v>930</v>
@@ -14700,7 +14846,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C201">
         <v>826</v>
@@ -14765,7 +14911,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C202">
         <v>1153</v>
@@ -14830,7 +14976,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="C203">
         <v>1122</v>
@@ -14895,7 +15041,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="C204">
         <v>1069</v>
@@ -14960,7 +15106,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C205">
         <v>1125</v>
@@ -15025,7 +15171,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C206">
         <v>1015</v>
@@ -15090,7 +15236,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C207">
         <v>1077</v>
@@ -15155,7 +15301,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C208">
         <v>673</v>
@@ -15220,7 +15366,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="C209">
         <v>885</v>
@@ -15285,7 +15431,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C210">
         <v>802</v>
@@ -15350,7 +15496,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C211">
         <v>1147</v>
@@ -15415,7 +15561,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C212">
         <v>1017</v>
@@ -15480,7 +15626,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C213">
         <v>1093</v>
@@ -15545,7 +15691,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C214">
         <v>886</v>
@@ -15610,7 +15756,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C215">
         <v>1054</v>
@@ -15675,7 +15821,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C216">
         <v>853</v>
@@ -15740,7 +15886,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C217">
         <v>1080</v>
@@ -15805,7 +15951,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="C218">
         <v>1129</v>
@@ -15870,7 +16016,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="C219">
         <v>1139</v>
@@ -15935,7 +16081,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C220">
         <v>1079</v>
@@ -16000,7 +16146,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C221">
         <v>1052</v>
@@ -16065,7 +16211,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="C222">
         <v>1014</v>
@@ -16130,7 +16276,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C223">
         <v>1185</v>
@@ -16195,7 +16341,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="C224">
         <v>1123</v>
@@ -16260,7 +16406,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="C225">
         <v>1006</v>
@@ -16325,7 +16471,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C226">
         <v>1185</v>
@@ -16390,7 +16536,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="C227">
         <v>843</v>
@@ -16455,7 +16601,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C228">
         <v>1131</v>
@@ -16520,7 +16666,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="C229">
         <v>978</v>
@@ -16585,7 +16731,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C230">
         <v>1124</v>
@@ -16650,7 +16796,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C231">
         <v>1176</v>
@@ -16715,7 +16861,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="C232">
         <v>1193</v>
@@ -16780,7 +16926,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C233">
         <v>836</v>
@@ -16845,7 +16991,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C234">
         <v>1049</v>
@@ -16910,7 +17056,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C235">
         <v>1161</v>
@@ -16975,7 +17121,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C236">
         <v>911</v>
@@ -17040,7 +17186,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>1074</v>
@@ -17105,7 +17251,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="C238">
         <v>1210</v>
@@ -17170,7 +17316,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>939</v>
@@ -17235,7 +17381,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C240">
         <v>1172</v>
@@ -17300,7 +17446,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C241">
         <v>1119</v>
@@ -17365,7 +17511,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C242">
         <v>1005</v>
@@ -17430,7 +17576,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C243">
         <v>1067</v>
@@ -17495,7 +17641,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="C244">
         <v>1150</v>
@@ -17560,7 +17706,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C245">
         <v>1215</v>
@@ -17625,7 +17771,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="C246">
         <v>1059</v>
@@ -17690,7 +17836,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C247">
         <v>917</v>
@@ -17755,7 +17901,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C248">
         <v>1105</v>
@@ -17820,7 +17966,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C249">
         <v>1177</v>
@@ -17885,7 +18031,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C250">
         <v>1160</v>
@@ -17950,7 +18096,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C251">
         <v>1142</v>
@@ -18015,7 +18161,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C252">
         <v>1140</v>
@@ -18080,7 +18226,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C253">
         <v>1143</v>
@@ -18145,7 +18291,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C254">
         <v>1077</v>
@@ -18210,7 +18356,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C255">
         <v>1041</v>
@@ -18275,7 +18421,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="C256">
         <v>1103</v>
@@ -18340,7 +18486,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C257">
         <v>1129</v>
@@ -18405,7 +18551,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="C258">
         <v>965</v>
@@ -18470,7 +18616,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C259">
         <v>1029</v>
@@ -18535,7 +18681,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C260">
         <v>725</v>
@@ -18600,7 +18746,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C261">
         <v>1055</v>
@@ -18665,7 +18811,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="C262">
         <v>1153</v>
@@ -18730,7 +18876,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C263">
         <v>1088</v>
@@ -18795,7 +18941,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C264">
         <v>1157</v>
@@ -18860,7 +19006,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C265">
         <v>951</v>
@@ -18925,7 +19071,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="C266">
         <v>944</v>
@@ -18990,7 +19136,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="C267">
         <v>814</v>
@@ -19055,7 +19201,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C268">
         <v>844</v>
@@ -19120,7 +19266,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="C269">
         <v>794</v>
@@ -19185,7 +19331,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="C270">
         <v>944</v>
@@ -19250,7 +19396,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C271">
         <v>947</v>
@@ -19315,7 +19461,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="C272">
         <v>1164</v>
@@ -19380,7 +19526,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="C273">
         <v>1239</v>
@@ -19445,7 +19591,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="C274">
         <v>1130</v>
@@ -19510,7 +19656,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C275">
         <v>1058</v>
@@ -19575,7 +19721,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="C276">
         <v>882</v>
@@ -19640,7 +19786,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C277">
         <v>936</v>
@@ -19705,7 +19851,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C278">
         <v>943</v>
@@ -19770,7 +19916,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C279">
         <v>862</v>
@@ -19835,7 +19981,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="C280">
         <v>963</v>
@@ -19900,7 +20046,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C281">
         <v>1011</v>
@@ -19965,7 +20111,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C282">
         <v>534</v>
@@ -20030,7 +20176,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C283">
         <v>591</v>
@@ -20095,7 +20241,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C284">
         <v>962</v>
@@ -20160,7 +20306,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="C285">
         <v>978</v>
@@ -20225,7 +20371,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C286">
         <v>908</v>
@@ -20290,7 +20436,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C287">
         <v>1016</v>
@@ -20355,7 +20501,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C288">
         <v>834</v>
@@ -20420,7 +20566,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="C289">
         <v>1136</v>
@@ -20485,7 +20631,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="C290">
         <v>1083</v>
@@ -20550,7 +20696,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C291">
         <v>1051</v>
@@ -20615,7 +20761,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C292">
         <v>913</v>
@@ -20680,7 +20826,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="C293">
         <v>1140</v>
@@ -20745,7 +20891,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="C294">
         <v>1032</v>
@@ -20810,7 +20956,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C295">
         <v>1142</v>
@@ -20875,7 +21021,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="C296">
         <v>1118</v>
@@ -20940,7 +21086,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="C297">
         <v>1147</v>
@@ -21005,7 +21151,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="C298">
         <v>981</v>
@@ -21070,7 +21216,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C299">
         <v>1100</v>
@@ -21135,7 +21281,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="C300">
         <v>1165</v>
@@ -21200,7 +21346,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C301">
         <v>1083</v>
@@ -21265,7 +21411,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="C302">
         <v>1218</v>
@@ -21330,7 +21476,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C303">
         <v>1031</v>
@@ -21395,7 +21541,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="C304">
         <v>1076</v>
@@ -21460,7 +21606,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="C305">
         <v>1097</v>
@@ -21525,7 +21671,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="C306">
         <v>1148</v>
@@ -21590,7 +21736,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="C307">
         <v>1025</v>
@@ -21655,7 +21801,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="C308">
         <v>1092</v>
@@ -21720,7 +21866,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="C309">
         <v>1064</v>
@@ -21785,7 +21931,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="C310">
         <v>1172</v>
@@ -21850,7 +21996,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C311">
         <v>951</v>
@@ -21915,7 +22061,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C312">
         <v>781</v>
@@ -21980,7 +22126,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="C313">
         <v>1094</v>
@@ -22045,7 +22191,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="C314">
         <v>898</v>
@@ -22110,7 +22256,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="C315">
         <v>1012</v>
@@ -22175,7 +22321,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C316">
         <v>1007</v>
@@ -22240,7 +22386,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="C317">
         <v>1004</v>
@@ -22305,7 +22451,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="C318">
         <v>850</v>
@@ -22370,7 +22516,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C319">
         <v>1032</v>
@@ -22435,7 +22581,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="C320">
         <v>948</v>
@@ -22500,7 +22646,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="C321">
         <v>1146</v>
@@ -22565,7 +22711,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="C322">
         <v>792</v>
@@ -22630,7 +22776,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="C323">
         <v>947</v>
@@ -22695,7 +22841,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C324">
         <v>1239</v>
@@ -22760,7 +22906,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="C325">
         <v>1231</v>
@@ -22825,7 +22971,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="C326">
         <v>1099</v>
@@ -22890,7 +23036,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="C327">
         <v>641</v>
@@ -22955,7 +23101,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C328">
         <v>1099</v>
@@ -23020,7 +23166,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="C329">
         <v>1187</v>
@@ -23085,7 +23231,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="C330">
         <v>931</v>
@@ -23150,7 +23296,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C331">
         <v>912</v>
@@ -23215,7 +23361,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="C332">
         <v>928</v>
@@ -23280,7 +23426,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="C333">
         <v>1140</v>
@@ -23345,7 +23491,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C334">
         <v>1213</v>
@@ -23410,7 +23556,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="C335">
         <v>831</v>
@@ -23475,7 +23621,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="C336">
         <v>850</v>
@@ -23540,7 +23686,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="C337">
         <v>1201</v>
@@ -23605,7 +23751,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C338">
         <v>800</v>
@@ -23670,7 +23816,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="C339">
         <v>836</v>
@@ -23735,7 +23881,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="C340">
         <v>1191</v>
@@ -23800,7 +23946,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C341">
         <v>938</v>
@@ -23865,7 +24011,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="C342">
         <v>1180</v>
@@ -23930,7 +24076,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="C343">
         <v>1119</v>
@@ -23995,7 +24141,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C344">
         <v>1115</v>
@@ -24060,7 +24206,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="C345">
         <v>1177</v>
@@ -24125,7 +24271,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="C346">
         <v>947</v>
@@ -24190,7 +24336,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="C347">
         <v>845</v>
@@ -24255,7 +24401,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="C348">
         <v>837</v>
@@ -24320,7 +24466,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="C349">
         <v>800</v>
@@ -24385,7 +24531,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="C350">
         <v>837</v>
@@ -24450,7 +24596,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C351">
         <v>624</v>
@@ -24515,7 +24661,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="C352">
         <v>403</v>
@@ -24580,7 +24726,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="C353">
         <v>969</v>
@@ -24645,7 +24791,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="C354">
         <v>1132</v>
@@ -24710,7 +24856,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="C355">
         <v>602</v>
@@ -24775,7 +24921,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="C356">
         <v>893</v>
@@ -24840,7 +24986,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="C357">
         <v>671</v>
@@ -24905,7 +25051,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="C358">
         <v>675</v>
@@ -24970,7 +25116,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="C359">
         <v>655</v>
@@ -25035,7 +25181,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="C360">
         <v>702</v>
@@ -25100,7 +25246,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C361">
         <v>635</v>
@@ -25165,7 +25311,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C362">
         <v>884</v>
@@ -25230,7 +25376,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="C363">
         <v>1176</v>
@@ -25295,7 +25441,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C364">
         <v>741</v>
@@ -25360,7 +25506,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C365">
         <v>1052</v>
@@ -25425,7 +25571,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="C366">
         <v>673</v>
@@ -25490,7 +25636,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="C367">
         <v>1165</v>
@@ -25555,7 +25701,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="C368">
         <v>678</v>
@@ -25620,7 +25766,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C369">
         <v>904</v>
@@ -25685,7 +25831,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="C370">
         <v>660</v>
@@ -25750,7 +25896,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="C371">
         <v>1028</v>
@@ -25815,7 +25961,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C372">
         <v>1082</v>
@@ -25880,7 +26026,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C373">
         <v>1141</v>
@@ -25945,7 +26091,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C374">
         <v>1216</v>
@@ -26010,7 +26156,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C375">
         <v>888</v>
@@ -26075,7 +26221,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="C376">
         <v>768</v>
@@ -26140,7 +26286,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C377">
         <v>1068</v>
@@ -26205,7 +26351,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="C378">
         <v>1057</v>
@@ -26270,7 +26416,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="C379">
         <v>1059</v>
@@ -26335,7 +26481,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="C380">
         <v>1106</v>
@@ -26400,7 +26546,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C381">
         <v>1002</v>
@@ -26465,7 +26611,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C382">
         <v>905</v>
@@ -26530,7 +26676,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C383">
         <v>437</v>
@@ -26595,7 +26741,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="C384">
         <v>669</v>
@@ -26660,7 +26806,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="C385">
         <v>870</v>
@@ -26725,7 +26871,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="C386">
         <v>666</v>
@@ -26790,7 +26936,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="C387">
         <v>1086</v>
@@ -26855,7 +27001,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="C388">
         <v>1187</v>
@@ -26920,7 +27066,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="C389">
         <v>1159</v>
@@ -26985,7 +27131,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="C390">
         <v>747</v>
@@ -27050,7 +27196,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="C391">
         <v>687</v>
@@ -27115,7 +27261,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C392">
         <v>625</v>
@@ -27180,7 +27326,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="C393">
         <v>1226</v>
@@ -27245,7 +27391,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="C394">
         <v>1062</v>
@@ -27310,7 +27456,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="C395">
         <v>771</v>
@@ -27375,7 +27521,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="C396">
         <v>710</v>
@@ -27440,7 +27586,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="C397">
         <v>1118</v>
@@ -27505,7 +27651,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="C398">
         <v>1010</v>
@@ -27570,7 +27716,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="C399">
         <v>984</v>
@@ -27635,7 +27781,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="C400">
         <v>1050</v>
@@ -27700,7 +27846,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C401">
         <v>783</v>
@@ -27765,7 +27911,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C402">
         <v>992</v>
@@ -27830,7 +27976,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="C403">
         <v>1199</v>
@@ -27895,7 +28041,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="C404">
         <v>1084</v>
@@ -27960,7 +28106,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="C405">
         <v>1200</v>
@@ -28025,7 +28171,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C406">
         <v>979</v>
@@ -28090,7 +28236,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="C407">
         <v>1114</v>
@@ -28155,7 +28301,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C408">
         <v>1030</v>
@@ -28220,7 +28366,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="C409">
         <v>837</v>
@@ -28285,7 +28431,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="C410">
         <v>1228</v>
@@ -28350,7 +28496,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="C411">
         <v>1011</v>
@@ -28415,7 +28561,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="C412">
         <v>889</v>
@@ -28480,7 +28626,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="C413">
         <v>674</v>
@@ -28545,7 +28691,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="C414">
         <v>676</v>
@@ -28610,7 +28756,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="C415">
         <v>475</v>
@@ -28675,7 +28821,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="C416">
         <v>520</v>
@@ -28740,7 +28886,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="C417">
         <v>1192</v>
@@ -28805,7 +28951,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="C418">
         <v>1006</v>
@@ -28870,7 +29016,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="C419">
         <v>1151</v>
@@ -28935,7 +29081,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C420">
         <v>770</v>
@@ -29000,7 +29146,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C421">
         <v>589</v>
@@ -29065,7 +29211,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="C422">
         <v>983</v>
@@ -29130,7 +29276,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="C423">
         <v>923</v>
@@ -29195,7 +29341,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="C424">
         <v>988</v>
@@ -29260,7 +29406,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="C425">
         <v>630</v>
@@ -29325,7 +29471,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C426">
         <v>762</v>
@@ -29390,7 +29536,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="C427">
         <v>652</v>
@@ -29455,7 +29601,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="C428">
         <v>585</v>
@@ -29520,7 +29666,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="C429">
         <v>393</v>
@@ -29585,7 +29731,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="C430">
         <v>1049</v>
@@ -29650,7 +29796,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="C431">
         <v>900</v>
@@ -29715,7 +29861,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="C432">
         <v>809</v>
@@ -29780,7 +29926,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C433">
         <v>1084</v>
@@ -29845,7 +29991,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C434">
         <v>918</v>
@@ -29910,7 +30056,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="C435">
         <v>680</v>
@@ -29975,7 +30121,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="C436">
         <v>529</v>
@@ -30040,7 +30186,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="C437">
         <v>1152</v>
@@ -30105,7 +30251,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="C438">
         <v>1104</v>
@@ -30170,7 +30316,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="C439">
         <v>868</v>
@@ -30235,7 +30381,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C440">
         <v>1125</v>
@@ -30300,7 +30446,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="C441">
         <v>713</v>
@@ -30365,7 +30511,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="C442">
         <v>627</v>
@@ -30430,7 +30576,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="C443">
         <v>642</v>
@@ -30495,7 +30641,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="C444">
         <v>1195</v>
@@ -30560,7 +30706,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="C445">
         <v>1159</v>
@@ -30625,7 +30771,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="C446">
         <v>820</v>
@@ -30690,7 +30836,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="C447">
         <v>667</v>
@@ -30755,7 +30901,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="C448">
         <v>958</v>
@@ -30820,7 +30966,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="C449">
         <v>897</v>
@@ -30885,7 +31031,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="C450">
         <v>351</v>
